--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_359_R36.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_359_R36.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1252</v>
+        <v>7.4928</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5035</v>
+        <v>3.1064</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6217</v>
+        <v>4.3864</v>
       </c>
       <c r="G2" t="n">
         <v>2.5945</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>1.907</v>
+        <v>1.2746</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5351</v>
+        <v>0.1379</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3719</v>
+        <v>1.1367</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7067</v>
+        <v>6.9596</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1772</v>
+        <v>2.9596</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5295</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3367</v>
@@ -688,13 +688,13 @@
         <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7635</v>
+        <v>0.4894</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1123</v>
+        <v>-0.3299</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3488</v>
+        <v>0.8193</v>
       </c>
       <c r="V3" t="n">
         <v>6.575</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4465</v>
+        <v>3.74</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2734</v>
+        <v>-0.0808</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7199</v>
+        <v>3.8208</v>
       </c>
       <c r="G4" t="n">
         <v>1.7197</v>
@@ -766,13 +766,13 @@
         <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4406</v>
+        <v>0.7341</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6247</v>
+        <v>-0.4321</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0653</v>
+        <v>1.1661</v>
       </c>
       <c r="V4" t="n">
         <v>1.7501</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>S. LARKIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4348</v>
+        <v>2.2814</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.917</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7518</v>
+        <v>1.3643</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8767</v>
+        <v>0.4372</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2112</v>
+        <v>-0.4093</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3345</v>
+        <v>0.8465</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1662</v>
+        <v>0.83</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1294</v>
+        <v>-0.7023</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0368</v>
+        <v>1.5324</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2895</v>
+        <v>-0.3929</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0818</v>
+        <v>0.293</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3713</v>
+        <v>-0.6859</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0941</v>
+        <v>0.2359</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9085</v>
+        <v>-0.3615</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1857</v>
+        <v>0.5975</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. LARKIN</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8364</v>
+        <v>2.0885</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6065</v>
+        <v>-0.0247</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2299</v>
+        <v>2.1132</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4372</v>
+        <v>0.8767</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4093</v>
+        <v>1.2112</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8465</v>
+        <v>-0.3345</v>
       </c>
       <c r="J6" t="n">
-        <v>0.83</v>
+        <v>1.1662</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7023</v>
+        <v>1.1294</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5324</v>
+        <v>0.0368</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3929</v>
+        <v>-0.2895</v>
       </c>
       <c r="N6" t="n">
-        <v>0.293</v>
+        <v>0.0818</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6859</v>
+        <v>-0.3713</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2091</v>
+        <v>0.7479</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6721</v>
+        <v>0.2008</v>
       </c>
       <c r="U6" t="n">
-        <v>0.463</v>
+        <v>0.5472</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.821</v>
+        <v>0.4164</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7019</v>
+        <v>0.2301</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1191</v>
+        <v>0.1863</v>
       </c>
       <c r="G7" t="n">
         <v>0.4459</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1432</v>
+        <v>-0.2614</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4129</v>
+        <v>-0.0589</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2697</v>
+        <v>-0.2025</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.032</v>
+        <v>0.0256</v>
       </c>
       <c r="E8" t="n">
-        <v>0.333</v>
+        <v>0.2898</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.365</v>
+        <v>-0.2642</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2797</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4643</v>
+        <v>0.5219</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.326</v>
+        <v>-0.3692</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7903</v>
+        <v>0.8911</v>
       </c>
       <c r="V8" t="n">
         <v>-1.6083</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9927</v>
+        <v>-0.8411999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3002</v>
+        <v>-1.1823</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3075</v>
+        <v>0.3411</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6338</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5909</v>
+        <v>-0.4393</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2921</v>
+        <v>-0.2585</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2663</v>
+        <v>-1.1985</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.3011</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3316</v>
+        <v>-1.4996</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3833</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2614</v>
+        <v>0.3293</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6348</v>
+        <v>0.4668</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6083</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. JONES</t>
+          <t>S. HAZER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.032</v>
+        <v>-3.0139</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2063</v>
+        <v>-3.4102</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8257</v>
+        <v>0.3963</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3724</v>
+        <v>-3.76</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7768</v>
+        <v>-4.4394</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5955</v>
+        <v>0.6793</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2251</v>
+        <v>-3.8813</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2619</v>
+        <v>-3.8813</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0368</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1473</v>
+        <v>0.1213</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5149</v>
+        <v>-0.5581</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6323</v>
+        <v>0.6793</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0876</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R11" t="n">
         <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4279</v>
+        <v>-0.4679</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3383</v>
+        <v>-0.5109</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0896</v>
+        <v>0.0431</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. HAZER</t>
+          <t>K. JONES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3842</v>
+        <v>-3.3694</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6461</v>
+        <v>-2.6782</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2618</v>
+        <v>-0.6913</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.76</v>
+        <v>-1.3724</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.4394</v>
+        <v>-0.7768</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6793</v>
+        <v>-0.5955</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.8813</v>
+        <v>-0.2251</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.8813</v>
+        <v>-0.2619</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.0368</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1213</v>
+        <v>-1.1473</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5581</v>
+        <v>-0.5149</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6793</v>
+        <v>-0.6323</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R12" t="n">
         <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8381999999999999</v>
+        <v>0.0905</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7468</v>
+        <v>-0.1336</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0914</v>
+        <v>0.224</v>
       </c>
       <c r="V12" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.8279</v>
+        <v>-7.3726</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.1873</v>
+        <v>-7.5975</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3593</v>
+        <v>0.2249</v>
       </c>
       <c r="G13" t="n">
         <v>-5.4159</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.644</v>
+        <v>-0.1887</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0455</v>
+        <v>-0.4558</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4015</v>
+        <v>0.2671</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.8355</v>
+        <v>7.2087</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.543000000000001</v>
+        <v>-7.169700000000001</v>
       </c>
       <c r="F14" t="n">
         <v>14.3782</v>
@@ -1537,7 +1537,7 @@
         <v>-2.6755</v>
       </c>
       <c r="P14" t="n">
-        <v>2.319599999999999</v>
+        <v>2.3196</v>
       </c>
       <c r="Q14" t="n">
         <v>-13.9173</v>
@@ -1546,13 +1546,13 @@
         <v>16.2368</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6928</v>
+        <v>3.0663</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.0047</v>
+        <v>-2.6315</v>
       </c>
       <c r="U14" t="n">
-        <v>5.6977</v>
+        <v>5.6979</v>
       </c>
       <c r="V14" t="n">
         <v>7.9308</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3891</v>
+        <v>1.5647</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2929</v>
+        <v>-0.061</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0962</v>
+        <v>1.6257</v>
       </c>
       <c r="G15" t="n">
         <v>1.0202</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3689</v>
+        <v>0.5445</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3462</v>
+        <v>-0.0077</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0227</v>
+        <v>0.5522</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.523</v>
+        <v>1.0582</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2458</v>
+        <v>-1.3638</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7688</v>
+        <v>2.422</v>
       </c>
       <c r="G16" t="n">
         <v>1.9756</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.1032</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4674</v>
+        <v>-0.5854</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0354</v>
+        <v>0.6886</v>
       </c>
       <c r="V16" t="n">
         <v>-0.7886</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.4635</v>
       </c>
       <c r="E17" t="n">
-        <v>0.221</v>
+        <v>-0.0149</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4448</v>
+        <v>0.4784</v>
       </c>
       <c r="G17" t="n">
         <v>0.8546</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0444</v>
+        <v>-0.2467</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2592</v>
+        <v>-0.4951</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2148</v>
+        <v>0.2484</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4139</v>
+        <v>-0.1273</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5836</v>
+        <v>-0.2298</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1697</v>
+        <v>0.1025</v>
       </c>
       <c r="G18" t="n">
         <v>1.0434</v>
@@ -1858,13 +1858,13 @@
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4419</v>
+        <v>-0.1553</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8883</v>
+        <v>-0.5344</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4463</v>
+        <v>0.3791</v>
       </c>
       <c r="V18" t="n">
         <v>1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>A. LAKIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7198</v>
+        <v>-0.5584</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3571</v>
+        <v>-1.1266</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6373</v>
+        <v>0.5682</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0998</v>
+        <v>0.9696</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2604</v>
+        <v>0.5213</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1605</v>
+        <v>0.4483</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2211</v>
+        <v>-0.1165</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4887</v>
+        <v>0.168</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2676</v>
+        <v>-0.2845</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1213</v>
+        <v>1.0861</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2283</v>
+        <v>0.3532</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.107</v>
+        <v>0.7328</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>0.148</v>
+        <v>-0.7057</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6721</v>
+        <v>-0.7782</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8202</v>
+        <v>0.0725</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. LAKIC</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3041</v>
+        <v>-0.9043</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2446</v>
+        <v>-2.2392</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0595</v>
+        <v>1.3348</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9696</v>
+        <v>-1.0998</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5213</v>
+        <v>-1.2604</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4483</v>
+        <v>0.1605</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1165</v>
+        <v>-1.2211</v>
       </c>
       <c r="K20" t="n">
-        <v>0.168</v>
+        <v>-1.4887</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2845</v>
+        <v>0.2676</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0861</v>
+        <v>0.1213</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3532</v>
+        <v>0.2283</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7328</v>
+        <v>-0.107</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4514</v>
+        <v>-0.0365</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8962</v>
+        <v>-0.5542</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5553</v>
+        <v>0.5177</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. MILTON</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3071</v>
+        <v>-0.9253</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9235</v>
+        <v>-3.4453</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2305</v>
+        <v>2.5201</v>
       </c>
       <c r="G21" t="n">
-        <v>3.5695</v>
+        <v>-0.1015</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9171</v>
+        <v>1.9364</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6524</v>
+        <v>-2.0378</v>
       </c>
       <c r="J21" t="n">
-        <v>3.9844</v>
+        <v>-1.3021</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8568</v>
+        <v>1.4151</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1275</v>
+        <v>-2.7172</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4148</v>
+        <v>1.2006</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0602</v>
+        <v>0.5213</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4751</v>
+        <v>0.6793</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8556</v>
+        <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2709</v>
+        <v>-0.4501</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0455</v>
+        <v>-0.664</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2254</v>
+        <v>0.2139</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.7501</v>
+        <v>-0.1418</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2862</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>S. MILTON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8739</v>
+        <v>-0.9374</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0351</v>
+        <v>0.9235</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1612</v>
+        <v>-1.8608</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1015</v>
+        <v>3.5695</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9364</v>
+        <v>2.9171</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0378</v>
+        <v>0.6524</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3021</v>
+        <v>3.9844</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4151</v>
+        <v>2.8568</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.7172</v>
+        <v>1.1275</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2006</v>
+        <v>-0.4148</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5213</v>
+        <v>0.0602</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6793</v>
+        <v>-0.4751</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.232</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3987</v>
+        <v>-0.9012</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2538</v>
+        <v>-1.0455</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.145</v>
+        <v>0.1443</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1418</v>
+        <v>-1.7501</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.214</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0717</v>
+        <v>-2.1002</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5573</v>
+        <v>-2.9111</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4856</v>
+        <v>0.8109</v>
       </c>
       <c r="G23" t="n">
         <v>-0.532</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0215</v>
+        <v>-0.0501</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.094</v>
+        <v>-0.4479</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0725</v>
+        <v>0.3978</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7501</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7227</v>
+        <v>-3.5826</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7921</v>
+        <v>-3.9101</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0694</v>
+        <v>0.3275</v>
       </c>
       <c r="G24" t="n">
         <v>-1.5917</v>
@@ -2326,13 +2326,13 @@
         <v>2.3195</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1489</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4674</v>
+        <v>-0.5854</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3185</v>
+        <v>0.5766</v>
       </c>
       <c r="V24" t="n">
         <v>-1.7501</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.8353</v>
+        <v>-6.049099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-14.3782</v>
+        <v>-14.3783</v>
       </c>
       <c r="F25" t="n">
-        <v>7.542999999999999</v>
+        <v>8.3293</v>
       </c>
       <c r="G25" t="n">
         <v>6.107900000000001</v>
@@ -2404,13 +2404,13 @@
         <v>13.9173</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.6928</v>
+        <v>-1.9067</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.6977</v>
+        <v>-5.6978</v>
       </c>
       <c r="U25" t="n">
-        <v>3.0047</v>
+        <v>3.7911</v>
       </c>
       <c r="V25" t="n">
         <v>-7.9308</v>
